--- a/dataset/complete_revision_process.xlsx
+++ b/dataset/complete_revision_process.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uapt33090-my.sharepoint.com/personal/rafaelgteixeira_ua_pt/Documents/BPs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3454" documentId="8_{FE27ECB8-01A8-4E17-A93E-53D153F1E55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E2433F4-7152-4934-8124-1D5A0BF61EB6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78E04F6D-2EF5-42BB-BA1F-636D2CA50AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" firstSheet="4" activeTab="4" xr2:uid="{6D78BA2D-CC13-4EEA-9445-74A6A7622CFA}"/>
   </bookViews>
@@ -20,6 +20,10 @@
     <sheet name="Finalsheet_cleaned" sheetId="7" r:id="rId5"/>
     <sheet name="Categories" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Filtered_categorized!$A$1:$AC$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Finalsheet_cleaned!$A$1:$AC$159</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3402,7 +3406,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3487,10 +3491,10 @@
     <xf numFmtId="0" fontId="18" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3526,14 +3530,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3580,7 +3576,15 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -8961,25 +8965,25 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A248:F1048576">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>$F248="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F247 A248:F1048576">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$F2="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F247">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$F2="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32 G36 G175">
-    <cfRule type="expression" dxfId="1" priority="7">
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>$G32="No"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>$G32="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25970,6 +25974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2D9072-6BC6-4898-8ADC-56F0A4E890B2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC170"/>
   <sheetFormatPr defaultRowHeight="14.65"/>
   <cols>
@@ -26012,26 +26017,26 @@
       </c>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="32" t="s">
         <v>768</v>
       </c>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
       <c r="X1" s="18" t="s">
         <v>769</v>
       </c>
-      <c r="Y1" s="32" t="s">
+      <c r="Y1" s="33" t="s">
         <v>770</v>
       </c>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
       <c r="AC1" s="17"/>
     </row>
     <row r="2" spans="1:29" s="11" customFormat="1" ht="68.25" customHeight="1">
@@ -26326,7 +26331,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="43.7">
+    <row r="6" spans="1:29" ht="45.75">
       <c r="A6" s="9" t="s">
         <v>16</v>
       </c>
@@ -26364,7 +26369,7 @@
         <v>67</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>9</v>
@@ -26412,7 +26417,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="16" customFormat="1" ht="72.95">
+    <row r="7" spans="1:29" s="16" customFormat="1" ht="76.5">
       <c r="A7" s="15" t="s">
         <v>19</v>
       </c>
@@ -26455,7 +26460,7 @@
       <c r="AB7" s="15"/>
       <c r="AC7" s="15"/>
     </row>
-    <row r="8" spans="1:29" ht="43.7">
+    <row r="8" spans="1:29" ht="45.75">
       <c r="A8" s="9" t="s">
         <v>22</v>
       </c>
@@ -26493,7 +26498,7 @@
         <v>67</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>9</v>
@@ -26627,7 +26632,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="43.7">
+    <row r="10" spans="1:29" ht="45.75">
       <c r="A10" s="9" t="s">
         <v>28</v>
       </c>
@@ -26665,7 +26670,7 @@
         <v>67</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>9</v>
@@ -26713,7 +26718,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="58.35">
+    <row r="11" spans="1:29" ht="60.75">
       <c r="A11" s="9" t="s">
         <v>31</v>
       </c>
@@ -26751,7 +26756,7 @@
         <v>67</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>9</v>
@@ -26799,7 +26804,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="43.7">
+    <row r="12" spans="1:29" ht="45.75">
       <c r="A12" s="9" t="s">
         <v>34</v>
       </c>
@@ -26837,7 +26842,7 @@
         <v>67</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>9</v>
@@ -26885,7 +26890,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="58.35">
+    <row r="13" spans="1:29" ht="60.75">
       <c r="A13" s="9" t="s">
         <v>37</v>
       </c>
@@ -26923,7 +26928,7 @@
         <v>67</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>9</v>
@@ -26971,7 +26976,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="58.35">
+    <row r="14" spans="1:29" ht="60.75">
       <c r="A14" s="9" t="s">
         <v>40</v>
       </c>
@@ -27009,7 +27014,7 @@
         <v>67</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>9</v>
@@ -27229,7 +27234,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="43.7">
+    <row r="17" spans="1:28" ht="45.75">
       <c r="A17" s="9" t="s">
         <v>49</v>
       </c>
@@ -27267,7 +27272,7 @@
         <v>67</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>9</v>
@@ -27315,7 +27320,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="43.7">
+    <row r="18" spans="1:28" ht="45.75">
       <c r="A18" s="9" t="s">
         <v>52</v>
       </c>
@@ -27353,7 +27358,7 @@
         <v>67</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>9</v>
@@ -27401,7 +27406,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="43.7">
+    <row r="19" spans="1:28" ht="45.75">
       <c r="A19" s="9" t="s">
         <v>55</v>
       </c>
@@ -27439,7 +27444,7 @@
         <v>67</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N19" s="9" t="s">
         <v>9</v>
@@ -27487,7 +27492,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="58.35">
+    <row r="20" spans="1:28" ht="76.5">
       <c r="A20" s="9" t="s">
         <v>58</v>
       </c>
@@ -27525,7 +27530,7 @@
         <v>67</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>9</v>
@@ -27573,7 +27578,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="43.7">
+    <row r="21" spans="1:28" ht="45.75">
       <c r="A21" s="9" t="s">
         <v>61</v>
       </c>
@@ -27611,7 +27616,7 @@
         <v>67</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>9</v>
@@ -27659,7 +27664,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="43.7">
+    <row r="22" spans="1:28" ht="45.75">
       <c r="A22" s="9" t="s">
         <v>68</v>
       </c>
@@ -27697,7 +27702,7 @@
         <v>67</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>9</v>
@@ -27745,7 +27750,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="43.7">
+    <row r="23" spans="1:28" ht="45.75">
       <c r="A23" s="9" t="s">
         <v>74</v>
       </c>
@@ -27783,7 +27788,7 @@
         <v>67</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>9</v>
@@ -27831,7 +27836,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="72.95">
+    <row r="24" spans="1:28" ht="76.5">
       <c r="A24" s="9" t="s">
         <v>77</v>
       </c>
@@ -27869,7 +27874,7 @@
         <v>67</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N24" s="9" t="s">
         <v>9</v>
@@ -27917,7 +27922,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="43.7">
+    <row r="25" spans="1:28" ht="45.75">
       <c r="A25" s="9" t="s">
         <v>80</v>
       </c>
@@ -27955,7 +27960,7 @@
         <v>67</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N25" s="9" t="s">
         <v>9</v>
@@ -28003,7 +28008,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="43.7">
+    <row r="26" spans="1:28" ht="45.75">
       <c r="A26" s="9" t="s">
         <v>87</v>
       </c>
@@ -28041,7 +28046,7 @@
         <v>67</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N26" s="9" t="s">
         <v>9</v>
@@ -28089,7 +28094,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="43.7">
+    <row r="27" spans="1:28" ht="45.75">
       <c r="A27" s="9" t="s">
         <v>90</v>
       </c>
@@ -28127,7 +28132,7 @@
         <v>67</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>9</v>
@@ -28175,7 +28180,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="58.35">
+    <row r="28" spans="1:28" ht="76.5">
       <c r="A28" s="9" t="s">
         <v>93</v>
       </c>
@@ -28213,7 +28218,7 @@
         <v>728</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>9</v>
@@ -28261,7 +28266,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="43.7">
+    <row r="29" spans="1:28" ht="45.75">
       <c r="A29" s="9" t="s">
         <v>96</v>
       </c>
@@ -28299,7 +28304,7 @@
         <v>67</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N29" s="9" t="s">
         <v>9</v>
@@ -28347,7 +28352,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="43.7">
+    <row r="30" spans="1:28" ht="45.75">
       <c r="A30" s="9" t="s">
         <v>99</v>
       </c>
@@ -28385,7 +28390,7 @@
         <v>67</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N30" s="9" t="s">
         <v>9</v>
@@ -28433,7 +28438,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="43.7">
+    <row r="31" spans="1:28" ht="45.75">
       <c r="A31" s="9" t="s">
         <v>102</v>
       </c>
@@ -28471,7 +28476,7 @@
         <v>67</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N31" s="9" t="s">
         <v>9</v>
@@ -28519,7 +28524,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="43.7">
+    <row r="32" spans="1:28" ht="45.75">
       <c r="A32" s="9" t="s">
         <v>105</v>
       </c>
@@ -28557,7 +28562,7 @@
         <v>67</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>9</v>
@@ -28605,7 +28610,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="43.7">
+    <row r="33" spans="1:28" ht="60.75">
       <c r="A33" s="9" t="s">
         <v>108</v>
       </c>
@@ -28643,7 +28648,7 @@
         <v>67</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N33" s="9" t="s">
         <v>9</v>
@@ -28691,7 +28696,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="72.95">
+    <row r="34" spans="1:28" ht="76.5">
       <c r="A34" s="9" t="s">
         <v>114</v>
       </c>
@@ -28729,7 +28734,7 @@
         <v>67</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N34" s="9" t="s">
         <v>9</v>
@@ -28777,7 +28782,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="43.7">
+    <row r="35" spans="1:28" ht="45.75">
       <c r="A35" s="9" t="s">
         <v>120</v>
       </c>
@@ -28815,7 +28820,7 @@
         <v>67</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N35" s="9" t="s">
         <v>9</v>
@@ -28863,7 +28868,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="43.7">
+    <row r="36" spans="1:28" ht="45.75">
       <c r="A36" s="9" t="s">
         <v>123</v>
       </c>
@@ -28901,7 +28906,7 @@
         <v>67</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>9</v>
@@ -29035,7 +29040,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="72.95">
+    <row r="38" spans="1:28" ht="76.5">
       <c r="A38" s="9" t="s">
         <v>129</v>
       </c>
@@ -29073,7 +29078,7 @@
         <v>67</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>9</v>
@@ -29207,7 +29212,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="43.7">
+    <row r="40" spans="1:28" ht="45.75">
       <c r="A40" s="9" t="s">
         <v>135</v>
       </c>
@@ -29245,7 +29250,7 @@
         <v>67</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N40" s="9" t="s">
         <v>9</v>
@@ -29293,7 +29298,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="58.35">
+    <row r="41" spans="1:28" ht="60.75">
       <c r="A41" s="9" t="s">
         <v>138</v>
       </c>
@@ -29331,7 +29336,7 @@
         <v>67</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>9</v>
@@ -29379,7 +29384,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="43.7">
+    <row r="42" spans="1:28" ht="45.75">
       <c r="A42" s="9" t="s">
         <v>144</v>
       </c>
@@ -29417,7 +29422,7 @@
         <v>728</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N42" s="9" t="s">
         <v>67</v>
@@ -29465,7 +29470,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="43.7">
+    <row r="43" spans="1:28" ht="45.75">
       <c r="A43" s="9" t="s">
         <v>147</v>
       </c>
@@ -29503,7 +29508,7 @@
         <v>67</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N43" s="9" t="s">
         <v>67</v>
@@ -29551,7 +29556,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="43.7">
+    <row r="44" spans="1:28" ht="45.75">
       <c r="A44" s="9" t="s">
         <v>150</v>
       </c>
@@ -29589,7 +29594,7 @@
         <v>728</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N44" s="9" t="s">
         <v>67</v>
@@ -29723,7 +29728,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="58.35">
+    <row r="46" spans="1:28" ht="60.75">
       <c r="A46" s="9" t="s">
         <v>159</v>
       </c>
@@ -29761,7 +29766,7 @@
         <v>728</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N46" s="9" t="s">
         <v>729</v>
@@ -29895,7 +29900,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="43.7">
+    <row r="48" spans="1:28" ht="45.75">
       <c r="A48" s="9" t="s">
         <v>168</v>
       </c>
@@ -29933,7 +29938,7 @@
         <v>728</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N48" s="9" t="s">
         <v>67</v>
@@ -29981,7 +29986,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="43.7">
+    <row r="49" spans="1:28" ht="45.75">
       <c r="A49" s="9" t="s">
         <v>177</v>
       </c>
@@ -30019,7 +30024,7 @@
         <v>728</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>67</v>
@@ -30067,7 +30072,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="43.7">
+    <row r="50" spans="1:28" ht="45.75">
       <c r="A50" s="9" t="s">
         <v>183</v>
       </c>
@@ -30105,7 +30110,7 @@
         <v>728</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>67</v>
@@ -30153,7 +30158,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="43.7">
+    <row r="51" spans="1:28" ht="45.75">
       <c r="A51" s="9" t="s">
         <v>192</v>
       </c>
@@ -30191,7 +30196,7 @@
         <v>728</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N51" s="9" t="s">
         <v>67</v>
@@ -30239,7 +30244,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="43.7">
+    <row r="52" spans="1:28" ht="45.75">
       <c r="A52" s="9" t="s">
         <v>195</v>
       </c>
@@ -30277,7 +30282,7 @@
         <v>9</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N52" s="9" t="s">
         <v>67</v>
@@ -30411,7 +30416,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="43.7">
+    <row r="54" spans="1:28" ht="45.75">
       <c r="A54" s="9" t="s">
         <v>202</v>
       </c>
@@ -30449,7 +30454,7 @@
         <v>728</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N54" s="9" t="s">
         <v>67</v>
@@ -30497,7 +30502,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="43.7">
+    <row r="55" spans="1:28" ht="45.75">
       <c r="A55" s="9" t="s">
         <v>205</v>
       </c>
@@ -30535,7 +30540,7 @@
         <v>67</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N55" s="9" t="s">
         <v>67</v>
@@ -30583,7 +30588,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="43.7">
+    <row r="56" spans="1:28" ht="45.75">
       <c r="A56" s="9" t="s">
         <v>208</v>
       </c>
@@ -30621,7 +30626,7 @@
         <v>728</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N56" s="9" t="s">
         <v>67</v>
@@ -30669,7 +30674,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="43.7">
+    <row r="57" spans="1:28" ht="45.75">
       <c r="A57" s="9" t="s">
         <v>211</v>
       </c>
@@ -30707,7 +30712,7 @@
         <v>67</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>67</v>
@@ -30755,7 +30760,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="43.7">
+    <row r="58" spans="1:28" ht="45.75">
       <c r="A58" s="9" t="s">
         <v>217</v>
       </c>
@@ -30793,7 +30798,7 @@
         <v>67</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N58" s="9" t="s">
         <v>67</v>
@@ -30841,7 +30846,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="43.7">
+    <row r="59" spans="1:28" ht="45.75">
       <c r="A59" s="9" t="s">
         <v>223</v>
       </c>
@@ -30879,7 +30884,7 @@
         <v>728</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N59" s="9" t="s">
         <v>67</v>
@@ -30927,7 +30932,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="43.7">
+    <row r="60" spans="1:28" ht="45.75">
       <c r="A60" s="9" t="s">
         <v>226</v>
       </c>
@@ -30965,7 +30970,7 @@
         <v>728</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N60" s="9" t="s">
         <v>67</v>
@@ -31013,7 +31018,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="58.35">
+    <row r="61" spans="1:28" ht="60.75">
       <c r="A61" s="9" t="s">
         <v>229</v>
       </c>
@@ -31051,7 +31056,7 @@
         <v>728</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N61" s="9" t="s">
         <v>67</v>
@@ -31099,7 +31104,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="43.7">
+    <row r="62" spans="1:28" ht="45.75">
       <c r="A62" s="9" t="s">
         <v>232</v>
       </c>
@@ -31137,7 +31142,7 @@
         <v>67</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N62" s="9" t="s">
         <v>67</v>
@@ -31185,7 +31190,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="43.7">
+    <row r="63" spans="1:28" ht="60.75">
       <c r="A63" s="9" t="s">
         <v>235</v>
       </c>
@@ -31223,7 +31228,7 @@
         <v>9</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N63" s="9" t="s">
         <v>9</v>
@@ -31271,7 +31276,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="58.35">
+    <row r="64" spans="1:28" ht="60.75">
       <c r="A64" s="9" t="s">
         <v>238</v>
       </c>
@@ -31309,7 +31314,7 @@
         <v>728</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N64" s="9" t="s">
         <v>67</v>
@@ -31357,7 +31362,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="43.7">
+    <row r="65" spans="1:29" ht="45.75">
       <c r="A65" s="9" t="s">
         <v>241</v>
       </c>
@@ -31395,7 +31400,7 @@
         <v>728</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N65" s="9" t="s">
         <v>67</v>
@@ -31443,7 +31448,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="43.7">
+    <row r="66" spans="1:29" ht="60.75">
       <c r="A66" s="9" t="s">
         <v>247</v>
       </c>
@@ -31481,7 +31486,7 @@
         <v>728</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N66" s="9" t="s">
         <v>67</v>
@@ -31529,7 +31534,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="43.7">
+    <row r="67" spans="1:29" ht="45.75">
       <c r="A67" s="9" t="s">
         <v>250</v>
       </c>
@@ -31567,7 +31572,7 @@
         <v>728</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N67" s="9" t="s">
         <v>729</v>
@@ -31615,7 +31620,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="43.7">
+    <row r="68" spans="1:29" ht="45.75">
       <c r="A68" s="9" t="s">
         <v>253</v>
       </c>
@@ -31653,7 +31658,7 @@
         <v>728</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N68" s="9" t="s">
         <v>67</v>
@@ -31701,7 +31706,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="58.35">
+    <row r="69" spans="1:29" ht="60.75">
       <c r="A69" s="9" t="s">
         <v>259</v>
       </c>
@@ -31739,142 +31744,142 @@
         <v>728</v>
       </c>
       <c r="M69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="S69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB69" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:29" s="16" customFormat="1" ht="45.75">
+      <c r="A70" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="B70" s="15">
+        <v>2022</v>
+      </c>
+      <c r="C70" s="15">
+        <v>13891286</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>772</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J70" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="K70" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="L70" s="15" t="s">
         <v>728</v>
       </c>
-      <c r="N69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="O69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q69" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="R69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="S69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="T69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="U69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="V69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="W69" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="X69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB69" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:29" s="48" customFormat="1" ht="45.75">
-      <c r="A70" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="B70" s="47">
-        <v>2022</v>
-      </c>
-      <c r="C70" s="47">
-        <v>13891286</v>
-      </c>
-      <c r="D70" s="47" t="s">
-        <v>272</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>273</v>
-      </c>
-      <c r="F70" s="47" t="s">
-        <v>772</v>
-      </c>
-      <c r="G70" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H70" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="I70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="J70" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="K70" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L70" s="47" t="s">
-        <v>728</v>
-      </c>
-      <c r="M70" s="47" t="s">
-        <v>728</v>
-      </c>
-      <c r="N70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="O70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="P70" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q70" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="R70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="S70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="T70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="U70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="V70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="W70" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="X70" s="47" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB70" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC70" s="47"/>
-    </row>
-    <row r="71" spans="1:29" ht="43.7">
+      <c r="M70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="O70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="P70" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q70" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="R70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="S70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="T70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="U70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="V70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="W70" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="X70" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC70" s="15"/>
+    </row>
+    <row r="71" spans="1:29" ht="45.75">
       <c r="A71" s="9" t="s">
         <v>277</v>
       </c>
@@ -31912,7 +31917,7 @@
         <v>728</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N71" s="9" t="s">
         <v>67</v>
@@ -32087,7 +32092,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="58.35">
+    <row r="74" spans="1:29" ht="60.75">
       <c r="A74" s="9" t="s">
         <v>292</v>
       </c>
@@ -32125,7 +32130,7 @@
         <v>728</v>
       </c>
       <c r="M74" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N74" s="9" t="s">
         <v>67</v>
@@ -32431,7 +32436,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="43.7">
+    <row r="78" spans="1:29" ht="45.75">
       <c r="A78" s="9" t="s">
         <v>313</v>
       </c>
@@ -32469,7 +32474,7 @@
         <v>728</v>
       </c>
       <c r="M78" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N78" s="9" t="s">
         <v>67</v>
@@ -32689,7 +32694,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="43.7">
+    <row r="81" spans="1:29" ht="45.75">
       <c r="A81" s="9" t="s">
         <v>325</v>
       </c>
@@ -32727,7 +32732,7 @@
         <v>728</v>
       </c>
       <c r="M81" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N81" s="9" t="s">
         <v>67</v>
@@ -32775,7 +32780,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="43.7">
+    <row r="82" spans="1:29" ht="45.75">
       <c r="A82" s="9" t="s">
         <v>328</v>
       </c>
@@ -32813,7 +32818,7 @@
         <v>728</v>
       </c>
       <c r="M82" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N82" s="9" t="s">
         <v>67</v>
@@ -32861,7 +32866,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="43.7">
+    <row r="83" spans="1:29" ht="45.75">
       <c r="A83" s="9" t="s">
         <v>331</v>
       </c>
@@ -32899,7 +32904,7 @@
         <v>728</v>
       </c>
       <c r="M83" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N83" s="9" t="s">
         <v>67</v>
@@ -33119,7 +33124,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:29" s="14" customFormat="1" ht="43.7">
+    <row r="86" spans="1:29" s="14" customFormat="1" ht="43.7" hidden="1">
       <c r="A86" s="13" t="s">
         <v>340</v>
       </c>
@@ -33246,7 +33251,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="43.7">
+    <row r="88" spans="1:29" ht="45.75">
       <c r="A88" s="9" t="s">
         <v>346</v>
       </c>
@@ -33284,7 +33289,7 @@
         <v>728</v>
       </c>
       <c r="M88" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N88" s="9" t="s">
         <v>67</v>
@@ -33418,7 +33423,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:29" s="14" customFormat="1" ht="43.7">
+    <row r="90" spans="1:29" s="14" customFormat="1" ht="43.7" hidden="1">
       <c r="A90" s="13" t="s">
         <v>355</v>
       </c>
@@ -33545,7 +33550,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="43.7">
+    <row r="92" spans="1:29" ht="60.75">
       <c r="A92" s="9" t="s">
         <v>364</v>
       </c>
@@ -33583,7 +33588,7 @@
         <v>728</v>
       </c>
       <c r="M92" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N92" s="9" t="s">
         <v>67</v>
@@ -33889,7 +33894,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="43.7">
+    <row r="96" spans="1:29" ht="45.75">
       <c r="A96" s="9" t="s">
         <v>386</v>
       </c>
@@ -33927,7 +33932,7 @@
         <v>728</v>
       </c>
       <c r="M96" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N96" s="9" t="s">
         <v>67</v>
@@ -34147,7 +34152,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="29.1">
+    <row r="99" spans="1:29" ht="30.75">
       <c r="A99" s="9" t="s">
         <v>422</v>
       </c>
@@ -34185,7 +34190,7 @@
         <v>728</v>
       </c>
       <c r="M99" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N99" s="9" t="s">
         <v>9</v>
@@ -34233,7 +34238,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="43.7">
+    <row r="100" spans="1:29" ht="45.75">
       <c r="A100" s="9" t="s">
         <v>425</v>
       </c>
@@ -34271,7 +34276,7 @@
         <v>728</v>
       </c>
       <c r="M100" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N100" s="9" t="s">
         <v>729</v>
@@ -34491,7 +34496,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="43.7">
+    <row r="103" spans="1:29" ht="45.75">
       <c r="A103" s="9" t="s">
         <v>437</v>
       </c>
@@ -34529,7 +34534,7 @@
         <v>728</v>
       </c>
       <c r="M103" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N103" s="9" t="s">
         <v>67</v>
@@ -34663,7 +34668,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="29.1">
+    <row r="105" spans="1:29" ht="30.75">
       <c r="A105" s="9" t="s">
         <v>449</v>
       </c>
@@ -34701,7 +34706,7 @@
         <v>728</v>
       </c>
       <c r="M105" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N105" s="9" t="s">
         <v>67</v>
@@ -34749,7 +34754,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="29.1">
+    <row r="106" spans="1:29" ht="30.75">
       <c r="A106" s="9" t="s">
         <v>464</v>
       </c>
@@ -34787,7 +34792,7 @@
         <v>728</v>
       </c>
       <c r="M106" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N106" s="9" t="s">
         <v>67</v>
@@ -34835,7 +34840,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="43.7">
+    <row r="107" spans="1:29" ht="45.75">
       <c r="A107" s="9" t="s">
         <v>476</v>
       </c>
@@ -34873,7 +34878,7 @@
         <v>728</v>
       </c>
       <c r="M107" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N107" s="9" t="s">
         <v>67</v>
@@ -34921,7 +34926,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="108" spans="1:29" s="14" customFormat="1" ht="58.35">
+    <row r="108" spans="1:29" s="14" customFormat="1" ht="58.35" hidden="1">
       <c r="A108" s="13" t="s">
         <v>482</v>
       </c>
@@ -34962,7 +34967,7 @@
       <c r="AB108" s="13"/>
       <c r="AC108" s="13"/>
     </row>
-    <row r="109" spans="1:29" ht="72.95">
+    <row r="109" spans="1:29" ht="76.5">
       <c r="A109" s="9" t="s">
         <v>485</v>
       </c>
@@ -35000,7 +35005,7 @@
         <v>728</v>
       </c>
       <c r="M109" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N109" s="9" t="s">
         <v>67</v>
@@ -35048,7 +35053,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="43.7">
+    <row r="110" spans="1:29" ht="45.75">
       <c r="A110" s="9" t="s">
         <v>500</v>
       </c>
@@ -35086,7 +35091,7 @@
         <v>728</v>
       </c>
       <c r="M110" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N110" s="9" t="s">
         <v>67</v>
@@ -35392,7 +35397,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="43.7">
+    <row r="114" spans="1:29" ht="45.75">
       <c r="A114" s="9" t="s">
         <v>527</v>
       </c>
@@ -35430,7 +35435,7 @@
         <v>728</v>
       </c>
       <c r="M114" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N114" s="9" t="s">
         <v>67</v>
@@ -35908,7 +35913,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="29.1">
+    <row r="120" spans="1:29" ht="30.75">
       <c r="A120" s="9" t="s">
         <v>551</v>
       </c>
@@ -35946,7 +35951,7 @@
         <v>728</v>
       </c>
       <c r="M120" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N120" s="9" t="s">
         <v>67</v>
@@ -35994,7 +35999,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="43.7">
+    <row r="121" spans="1:29" ht="60.75">
       <c r="A121" s="9" t="s">
         <v>557</v>
       </c>
@@ -36032,7 +36037,7 @@
         <v>728</v>
       </c>
       <c r="M121" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N121" s="9" t="s">
         <v>9</v>
@@ -36166,7 +36171,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="29.1">
+    <row r="123" spans="1:29" ht="30.75">
       <c r="A123" s="9" t="s">
         <v>563</v>
       </c>
@@ -36204,7 +36209,7 @@
         <v>67</v>
       </c>
       <c r="M123" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N123" s="9" t="s">
         <v>67</v>
@@ -36252,7 +36257,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="58.35">
+    <row r="124" spans="1:29" ht="60.75">
       <c r="A124" s="9" t="s">
         <v>566</v>
       </c>
@@ -36290,7 +36295,7 @@
         <v>728</v>
       </c>
       <c r="M124" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N124" s="9" t="s">
         <v>67</v>
@@ -36338,7 +36343,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="125" spans="1:29" s="14" customFormat="1" ht="43.7">
+    <row r="125" spans="1:29" s="14" customFormat="1" ht="43.7" hidden="1">
       <c r="A125" s="13" t="s">
         <v>572</v>
       </c>
@@ -36379,7 +36384,7 @@
       <c r="AB125" s="13"/>
       <c r="AC125" s="13"/>
     </row>
-    <row r="126" spans="1:29" s="14" customFormat="1" ht="43.7">
+    <row r="126" spans="1:29" s="14" customFormat="1" ht="43.7" hidden="1">
       <c r="A126" s="13" t="s">
         <v>575</v>
       </c>
@@ -36592,7 +36597,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="129" spans="1:29" s="14" customFormat="1" ht="29.1">
+    <row r="129" spans="1:29" s="14" customFormat="1" ht="29.1" hidden="1">
       <c r="A129" s="13" t="s">
         <v>593</v>
       </c>
@@ -36633,7 +36638,7 @@
       <c r="AB129" s="13"/>
       <c r="AC129" s="13"/>
     </row>
-    <row r="130" spans="1:29" ht="43.7">
+    <row r="130" spans="1:29" ht="45.75">
       <c r="A130" s="9" t="s">
         <v>596</v>
       </c>
@@ -36671,7 +36676,7 @@
         <v>728</v>
       </c>
       <c r="M130" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N130" s="9" t="s">
         <v>67</v>
@@ -37063,7 +37068,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="43.7">
+    <row r="135" spans="1:29" ht="45.75">
       <c r="A135" s="9" t="s">
         <v>620</v>
       </c>
@@ -37101,7 +37106,7 @@
         <v>728</v>
       </c>
       <c r="M135" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N135" s="9" t="s">
         <v>67</v>
@@ -37149,7 +37154,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="43.7">
+    <row r="136" spans="1:29" ht="45.75">
       <c r="A136" s="9" t="s">
         <v>623</v>
       </c>
@@ -37187,7 +37192,7 @@
         <v>728</v>
       </c>
       <c r="M136" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N136" s="9" t="s">
         <v>67</v>
@@ -37235,7 +37240,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="43.7">
+    <row r="137" spans="1:29" ht="60.75">
       <c r="A137" s="9" t="s">
         <v>629</v>
       </c>
@@ -37273,7 +37278,7 @@
         <v>728</v>
       </c>
       <c r="M137" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N137" s="9" t="s">
         <v>67</v>
@@ -37321,7 +37326,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="58.35">
+    <row r="138" spans="1:29" ht="60.75">
       <c r="A138" s="9" t="s">
         <v>633</v>
       </c>
@@ -37359,7 +37364,7 @@
         <v>728</v>
       </c>
       <c r="M138" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N138" s="9" t="s">
         <v>67</v>
@@ -37493,7 +37498,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="58.35">
+    <row r="140" spans="1:29" ht="60.75">
       <c r="A140" s="9" t="s">
         <v>637</v>
       </c>
@@ -37531,7 +37536,7 @@
         <v>728</v>
       </c>
       <c r="M140" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N140" s="9" t="s">
         <v>67</v>
@@ -37579,7 +37584,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="58.35">
+    <row r="141" spans="1:29" ht="60.75">
       <c r="A141" s="9" t="s">
         <v>639</v>
       </c>
@@ -37617,7 +37622,7 @@
         <v>728</v>
       </c>
       <c r="M141" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N141" s="9" t="s">
         <v>67</v>
@@ -38009,7 +38014,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="146" spans="1:28" ht="43.7">
+    <row r="146" spans="1:28" ht="45.75">
       <c r="A146" s="9" t="s">
         <v>651</v>
       </c>
@@ -38047,7 +38052,7 @@
         <v>728</v>
       </c>
       <c r="M146" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N146" s="9" t="s">
         <v>67</v>
@@ -38267,7 +38272,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="149" spans="1:28" ht="43.7">
+    <row r="149" spans="1:28" ht="45.75">
       <c r="A149" s="9" t="s">
         <v>657</v>
       </c>
@@ -38305,7 +38310,7 @@
         <v>728</v>
       </c>
       <c r="M149" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N149" s="9" t="s">
         <v>67</v>
@@ -38525,7 +38530,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="152" spans="1:28" ht="58.35">
+    <row r="152" spans="1:28" ht="60.75">
       <c r="A152" s="9" t="s">
         <v>663</v>
       </c>
@@ -38563,7 +38568,7 @@
         <v>728</v>
       </c>
       <c r="M152" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N152" s="9" t="s">
         <v>67</v>
@@ -38783,7 +38788,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="155" spans="1:28" ht="43.7">
+    <row r="155" spans="1:28" ht="45.75">
       <c r="A155" s="9" t="s">
         <v>669</v>
       </c>
@@ -38821,7 +38826,7 @@
         <v>728</v>
       </c>
       <c r="M155" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N155" s="9" t="s">
         <v>67</v>
@@ -38869,7 +38874,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="156" spans="1:28" ht="29.1">
+    <row r="156" spans="1:28" ht="30.75">
       <c r="A156" s="9" t="s">
         <v>671</v>
       </c>
@@ -38907,7 +38912,7 @@
         <v>728</v>
       </c>
       <c r="M156" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N156" s="9" t="s">
         <v>67</v>
@@ -38955,7 +38960,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="157" spans="1:28" ht="43.7">
+    <row r="157" spans="1:28" ht="45.75">
       <c r="A157" s="9" t="s">
         <v>673</v>
       </c>
@@ -38993,7 +38998,7 @@
         <v>9</v>
       </c>
       <c r="M157" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N157" s="9" t="s">
         <v>67</v>
@@ -39041,7 +39046,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" spans="1:28" ht="58.35">
+    <row r="158" spans="1:28" ht="60.75">
       <c r="A158" s="9" t="s">
         <v>675</v>
       </c>
@@ -39079,7 +39084,7 @@
         <v>728</v>
       </c>
       <c r="M158" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N158" s="9" t="s">
         <v>67</v>
@@ -39127,7 +39132,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="159" spans="1:28" ht="58.35">
+    <row r="159" spans="1:28" ht="60.75">
       <c r="A159" s="9" t="s">
         <v>677</v>
       </c>
@@ -39165,7 +39170,7 @@
         <v>728</v>
       </c>
       <c r="M159" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N159" s="9" t="s">
         <v>9</v>
@@ -39213,7 +39218,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="160" spans="1:28" ht="43.7">
+    <row r="160" spans="1:28" ht="60.75">
       <c r="A160" s="9" t="s">
         <v>679</v>
       </c>
@@ -39251,7 +39256,7 @@
         <v>67</v>
       </c>
       <c r="M160" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N160" s="9" t="s">
         <v>67</v>
@@ -39385,7 +39390,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="162" spans="1:28" ht="43.7">
+    <row r="162" spans="1:28" ht="45.75">
       <c r="A162" s="9" t="s">
         <v>683</v>
       </c>
@@ -39423,7 +39428,7 @@
         <v>67</v>
       </c>
       <c r="M162" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N162" s="9" t="s">
         <v>67</v>
@@ -39471,7 +39476,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="163" spans="1:28" ht="58.35">
+    <row r="163" spans="1:28" ht="60.75">
       <c r="A163" s="9" t="s">
         <v>685</v>
       </c>
@@ -39509,7 +39514,7 @@
         <v>9</v>
       </c>
       <c r="M163" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N163" s="9" t="s">
         <v>67</v>
@@ -39557,7 +39562,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="164" spans="1:28" ht="58.35">
+    <row r="164" spans="1:28" ht="60.75">
       <c r="A164" s="9" t="s">
         <v>687</v>
       </c>
@@ -39595,7 +39600,7 @@
         <v>9</v>
       </c>
       <c r="M164" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N164" s="9" t="s">
         <v>729</v>
@@ -39901,7 +39906,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="168" spans="1:28" ht="58.35">
+    <row r="168" spans="1:28" ht="60.75">
       <c r="A168" s="9" t="s">
         <v>697</v>
       </c>
@@ -39939,7 +39944,7 @@
         <v>728</v>
       </c>
       <c r="M168" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N168" s="9" t="s">
         <v>9</v>
@@ -39987,7 +39992,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="169" spans="1:28" ht="43.7">
+    <row r="169" spans="1:28" ht="45.75">
       <c r="A169" s="9" t="s">
         <v>701</v>
       </c>
@@ -40025,7 +40030,7 @@
         <v>67</v>
       </c>
       <c r="M169" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N169" s="9" t="s">
         <v>67</v>
@@ -40073,7 +40078,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="170" spans="1:28" ht="43.7">
+    <row r="170" spans="1:28" ht="45.75">
       <c r="A170" s="9" t="s">
         <v>703</v>
       </c>
@@ -40111,7 +40116,7 @@
         <v>728</v>
       </c>
       <c r="M170" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N170" s="9" t="s">
         <v>9</v>
@@ -40160,17 +40165,38 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC170" xr:uid="{9F2D9072-6BC6-4898-8ADC-56F0A4E890B2}">
+    <filterColumn colId="6" showButton="0"/>
+    <filterColumn colId="7" showButton="0"/>
+    <filterColumn colId="8" showButton="0"/>
+    <filterColumn colId="9" showButton="0"/>
+    <filterColumn colId="11" showButton="0"/>
+    <filterColumn colId="12" showButton="0">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+    <filterColumn colId="14" showButton="0"/>
+    <filterColumn colId="15" showButton="0"/>
+    <filterColumn colId="16" showButton="0"/>
+    <filterColumn colId="17" showButton="0"/>
+    <filterColumn colId="18" showButton="0"/>
+    <filterColumn colId="19" showButton="0"/>
+    <filterColumn colId="20" showButton="0"/>
+    <filterColumn colId="21" showButton="0"/>
+    <filterColumn colId="24" showButton="0"/>
+    <filterColumn colId="25" showButton="0"/>
+    <filterColumn colId="26" showButton="0"/>
+  </autoFilter>
   <mergeCells count="10">
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="O1:W1"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="Y1:AB1"/>
-    <mergeCell ref="O1:W1"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576 N3:O1048576 R165:S165 H171:H1048576 H3:H169 I3:K1048576 P165 Q3:S164 Q166:S1048576 X3:X1048576" xr:uid="{D7455BF3-A317-47A3-B71A-E741B7FB6AE3}">
@@ -40278,26 +40304,26 @@
       </c>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="32" t="s">
         <v>768</v>
       </c>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
       <c r="X1" s="18" t="s">
         <v>769</v>
       </c>
-      <c r="Y1" s="32" t="s">
+      <c r="Y1" s="33" t="s">
         <v>770</v>
       </c>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
       <c r="AC1" s="17"/>
     </row>
     <row r="2" spans="1:29" s="11" customFormat="1" ht="68.25" customHeight="1">
@@ -40635,7 +40661,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="43.7">
+    <row r="6" spans="1:29" ht="45.75">
       <c r="A6" s="9" t="s">
         <v>22</v>
       </c>
@@ -40673,7 +40699,7 @@
         <v>67</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N6" s="9" t="s">
         <v>67</v>
@@ -40845,7 +40871,7 @@
         <v>67</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>728</v>
+        <v>9</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>67</v>
@@ -40931,7 +40957,7 @@
         <v>67</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>67</v>
@@ -41017,7 +41043,7 @@
         <v>67</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>67</v>
@@ -41103,7 +41129,7 @@
         <v>67</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>67</v>
@@ -41189,7 +41215,7 @@
         <v>67</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>67</v>
@@ -41447,7 +41473,7 @@
         <v>67</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>67</v>
@@ -41533,7 +41559,7 @@
         <v>67</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>729</v>
@@ -41705,7 +41731,7 @@
         <v>67</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N18" s="9" t="s">
         <v>67</v>
@@ -41791,7 +41817,7 @@
         <v>67</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N19" s="9" t="s">
         <v>67</v>
@@ -41877,7 +41903,7 @@
         <v>67</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N20" s="9" t="s">
         <v>67</v>
@@ -41963,7 +41989,7 @@
         <v>67</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>67</v>
@@ -42049,7 +42075,7 @@
         <v>67</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>67</v>
@@ -42135,7 +42161,7 @@
         <v>67</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>67</v>
@@ -42221,7 +42247,7 @@
         <v>67</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N24" s="9" t="s">
         <v>67</v>
@@ -42307,7 +42333,7 @@
         <v>67</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N25" s="9" t="s">
         <v>67</v>
@@ -42393,7 +42419,7 @@
         <v>67</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N26" s="9" t="s">
         <v>67</v>
@@ -42479,7 +42505,7 @@
         <v>67</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>67</v>
@@ -42565,7 +42591,7 @@
         <v>67</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>67</v>
@@ -42651,7 +42677,7 @@
         <v>67</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N29" s="9" t="s">
         <v>67</v>
@@ -42737,7 +42763,7 @@
         <v>67</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N30" s="9" t="s">
         <v>67</v>
@@ -42823,7 +42849,7 @@
         <v>67</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N31" s="9" t="s">
         <v>67</v>
@@ -42909,7 +42935,7 @@
         <v>67</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>67</v>
@@ -42995,7 +43021,7 @@
         <v>67</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N33" s="9" t="s">
         <v>67</v>
@@ -43081,7 +43107,7 @@
         <v>67</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N34" s="9" t="s">
         <v>67</v>
@@ -43253,7 +43279,7 @@
         <v>67</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>67</v>
@@ -43425,7 +43451,7 @@
         <v>67</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>67</v>
@@ -43511,7 +43537,7 @@
         <v>67</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N39" s="9" t="s">
         <v>67</v>
@@ -43683,7 +43709,7 @@
         <v>67</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>67</v>
@@ -43769,7 +43795,7 @@
         <v>67</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N42" s="9" t="s">
         <v>67</v>
@@ -43941,7 +43967,7 @@
         <v>67</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N44" s="9" t="s">
         <v>67</v>
@@ -44113,7 +44139,7 @@
         <v>67</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N46" s="9" t="s">
         <v>67</v>
@@ -44199,7 +44225,7 @@
         <v>67</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>67</v>
@@ -44285,7 +44311,7 @@
         <v>67</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N48" s="9" t="s">
         <v>67</v>
@@ -44333,7 +44359,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="45.75">
+    <row r="49" spans="1:28" ht="45.75">
       <c r="A49" s="9" t="s">
         <v>192</v>
       </c>
@@ -44371,7 +44397,7 @@
         <v>67</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N49" s="9" t="s">
         <v>67</v>
@@ -44419,7 +44445,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="45.75">
+    <row r="50" spans="1:28" ht="45.75">
       <c r="A50" s="9" t="s">
         <v>195</v>
       </c>
@@ -44457,7 +44483,7 @@
         <v>67</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>67</v>
@@ -44505,7 +44531,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="45.75">
+    <row r="51" spans="1:28" ht="45.75">
       <c r="A51" s="9" t="s">
         <v>198</v>
       </c>
@@ -44591,7 +44617,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="45.75">
+    <row r="52" spans="1:28" ht="45.75">
       <c r="A52" s="9" t="s">
         <v>202</v>
       </c>
@@ -44629,7 +44655,7 @@
         <v>67</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N52" s="9" t="s">
         <v>67</v>
@@ -44677,7 +44703,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="45.75">
+    <row r="53" spans="1:28" ht="45.75">
       <c r="A53" s="9" t="s">
         <v>205</v>
       </c>
@@ -44715,7 +44741,7 @@
         <v>67</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N53" s="9" t="s">
         <v>67</v>
@@ -44763,7 +44789,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="64.5" customHeight="1">
+    <row r="54" spans="1:28" ht="64.5" customHeight="1">
       <c r="A54" s="9" t="s">
         <v>208</v>
       </c>
@@ -44801,7 +44827,7 @@
         <v>67</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N54" s="9" t="s">
         <v>67</v>
@@ -44849,7 +44875,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="63" customHeight="1">
+    <row r="55" spans="1:28" ht="63" customHeight="1">
       <c r="A55" s="9" t="s">
         <v>211</v>
       </c>
@@ -44887,7 +44913,7 @@
         <v>67</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N55" s="9" t="s">
         <v>67</v>
@@ -44935,7 +44961,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="45.75">
+    <row r="56" spans="1:28" ht="45.75">
       <c r="A56" s="9" t="s">
         <v>217</v>
       </c>
@@ -44973,7 +44999,7 @@
         <v>67</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N56" s="9" t="s">
         <v>67</v>
@@ -45021,7 +45047,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="45.75">
+    <row r="57" spans="1:28" ht="45.75">
       <c r="A57" s="9" t="s">
         <v>223</v>
       </c>
@@ -45059,7 +45085,7 @@
         <v>67</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>67</v>
@@ -45107,7 +45133,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="45.75">
+    <row r="58" spans="1:28" ht="45.75">
       <c r="A58" s="9" t="s">
         <v>226</v>
       </c>
@@ -45145,7 +45171,7 @@
         <v>67</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N58" s="9" t="s">
         <v>67</v>
@@ -45193,7 +45219,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="60.75">
+    <row r="59" spans="1:28" ht="60.75">
       <c r="A59" s="9" t="s">
         <v>229</v>
       </c>
@@ -45231,7 +45257,7 @@
         <v>67</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N59" s="9" t="s">
         <v>67</v>
@@ -45279,7 +45305,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="45.75">
+    <row r="60" spans="1:28" ht="45.75">
       <c r="A60" s="9" t="s">
         <v>232</v>
       </c>
@@ -45317,7 +45343,7 @@
         <v>67</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N60" s="9" t="s">
         <v>67</v>
@@ -45365,7 +45391,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="60.75">
+    <row r="61" spans="1:28" ht="60.75">
       <c r="A61" s="9" t="s">
         <v>235</v>
       </c>
@@ -45403,7 +45429,7 @@
         <v>9</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N61" s="9" t="s">
         <v>67</v>
@@ -45451,1747 +45477,1727 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:29" s="46" customFormat="1" ht="60.75">
-      <c r="A62" s="45" t="s">
+    <row r="62" spans="1:28" ht="60.75">
+      <c r="A62" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="B62" s="45">
+      <c r="B62" s="9">
         <v>2024</v>
       </c>
-      <c r="C62" s="45">
+      <c r="C62" s="9">
         <v>24732400</v>
       </c>
-      <c r="D62" s="45" t="s">
+      <c r="D62" s="9" t="s">
         <v>239</v>
       </c>
       <c r="E62" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="F62" s="45" t="s">
+      <c r="F62" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="G62" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="I62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J62" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K62" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M62" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P62" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q62" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="S62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="T62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X62" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB62" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC62" s="45"/>
-    </row>
-    <row r="63" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A63" s="45" t="s">
+      <c r="G62" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K62" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P62" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q62" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="S62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X62" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB62" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" ht="45.75">
+      <c r="A63" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="B63" s="45">
+      <c r="B63" s="9">
         <v>2024</v>
       </c>
-      <c r="C63" s="45">
+      <c r="C63" s="9">
         <v>19391374</v>
       </c>
-      <c r="D63" s="45" t="s">
+      <c r="D63" s="9" t="s">
         <v>242</v>
       </c>
       <c r="E63" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="F63" s="45" t="s">
+      <c r="F63" s="9" t="s">
         <v>777</v>
       </c>
-      <c r="G63" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H63" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J63" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K63" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L63" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="M63" s="45" t="s">
+      <c r="G63" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O63" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="N63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O63" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="P63" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q63" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R63" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="S63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="T63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC63" s="45"/>
-    </row>
-    <row r="64" spans="1:29" s="46" customFormat="1" ht="60.75">
-      <c r="A64" s="45" t="s">
+      <c r="P63" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q63" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R63" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="S63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB63" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" ht="60.75">
+      <c r="A64" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B64" s="45">
+      <c r="B64" s="9">
         <v>2024</v>
       </c>
-      <c r="C64" s="45">
+      <c r="C64" s="9">
         <v>8908044</v>
       </c>
-      <c r="D64" s="45" t="s">
+      <c r="D64" s="9" t="s">
         <v>248</v>
       </c>
       <c r="E64" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="F64" s="45" t="s">
+      <c r="F64" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="G64" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H64" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="K64" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M64" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P64" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q64" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="S64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="T64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X64" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB64" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC64" s="45"/>
-    </row>
-    <row r="65" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A65" s="45" t="s">
+      <c r="G64" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K64" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P64" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q64" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="S64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X64" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB64" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" ht="45.75">
+      <c r="A65" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B65" s="45">
+      <c r="B65" s="9">
         <v>2024</v>
       </c>
-      <c r="C65" s="45">
+      <c r="C65" s="9">
         <v>15361233</v>
       </c>
-      <c r="D65" s="45" t="s">
+      <c r="D65" s="9" t="s">
         <v>251</v>
       </c>
       <c r="E65" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="F65" s="45" t="s">
+      <c r="F65" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="G65" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H65" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J65" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K65" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M65" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O65" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P65" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q65" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R65" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="S65" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="T65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB65" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC65" s="45"/>
-    </row>
-    <row r="66" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A66" s="45" t="s">
+      <c r="G65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="P65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="S65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="T65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB65" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" ht="45.75">
+      <c r="A66" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B66" s="45">
+      <c r="B66" s="9">
         <v>2023</v>
       </c>
-      <c r="C66" s="45">
+      <c r="C66" s="9">
         <v>1636804</v>
       </c>
-      <c r="D66" s="45" t="s">
+      <c r="D66" s="9" t="s">
         <v>254</v>
       </c>
       <c r="E66" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="F66" s="45" t="s">
+      <c r="F66" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="G66" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H66" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J66" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="K66" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="L66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M66" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P66" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q66" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R66" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="S66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="T66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W66" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X66" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB66" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC66" s="45"/>
-    </row>
-    <row r="67" spans="1:29" s="46" customFormat="1" ht="60.75">
-      <c r="A67" s="45" t="s">
+      <c r="G66" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="K66" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="L66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P66" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q66" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R66" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="S66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W66" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X66" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB66" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" ht="60.75">
+      <c r="A67" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B67" s="45">
+      <c r="B67" s="9">
         <v>2022</v>
       </c>
-      <c r="C67" s="45">
+      <c r="C67" s="9">
         <v>15361284</v>
       </c>
-      <c r="D67" s="45" t="s">
+      <c r="D67" s="9" t="s">
         <v>260</v>
       </c>
       <c r="E67" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="F67" s="45" t="s">
+      <c r="F67" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="G67" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="I67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="K67" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M67" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P67" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q67" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R67" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="S67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="T67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB67" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC67" s="45"/>
-    </row>
-    <row r="68" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A68" s="45" t="s">
+      <c r="G67" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K67" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P67" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q67" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R67" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="S67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB67" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" ht="45.75">
+      <c r="A68" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="B68" s="45">
+      <c r="B68" s="9">
         <v>2021</v>
       </c>
-      <c r="C68" s="45">
+      <c r="C68" s="9">
         <v>8908044</v>
       </c>
-      <c r="D68" s="45" t="s">
+      <c r="D68" s="9" t="s">
         <v>278</v>
       </c>
       <c r="E68" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="F68" s="45" t="s">
+      <c r="F68" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="G68" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H68" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="I68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J68" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="K68" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M68" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P68" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q68" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="S68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="T68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB68" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC68" s="45"/>
-    </row>
-    <row r="69" spans="1:29" s="46" customFormat="1" ht="60.75">
-      <c r="A69" s="45" t="s">
+      <c r="G68" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J68" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="K68" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P68" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q68" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="S68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA68" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB68" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28" ht="60.75">
+      <c r="A69" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="B69" s="45">
+      <c r="B69" s="9">
         <v>2021</v>
       </c>
-      <c r="C69" s="45">
+      <c r="C69" s="9">
         <v>23274662</v>
       </c>
-      <c r="D69" s="45" t="s">
+      <c r="D69" s="9" t="s">
         <v>287</v>
       </c>
       <c r="E69" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F69" s="45" t="s">
+      <c r="F69" s="9" t="s">
         <v>777</v>
       </c>
-      <c r="G69" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H69" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J69" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K69" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="L69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M69" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="N69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P69" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q69" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R69" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="S69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="T69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W69" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB69" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC69" s="45"/>
-    </row>
-    <row r="70" spans="1:29" s="46" customFormat="1" ht="60.75">
-      <c r="A70" s="45" t="s">
+      <c r="G69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K69" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="S69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB69" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" ht="60.75">
+      <c r="A70" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="B70" s="45">
+      <c r="B70" s="9">
         <v>2022</v>
       </c>
-      <c r="C70" s="45">
+      <c r="C70" s="9">
         <v>21622337</v>
       </c>
-      <c r="D70" s="45" t="s">
+      <c r="D70" s="9" t="s">
         <v>293</v>
       </c>
       <c r="E70" s="29" t="s">
         <v>294</v>
       </c>
-      <c r="F70" s="45" t="s">
+      <c r="F70" s="9" t="s">
         <v>772</v>
       </c>
-      <c r="G70" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H70" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J70" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K70" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M70" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O70" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="P70" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q70" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R70" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="S70" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="T70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W70" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X70" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB70" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC70" s="45"/>
-    </row>
-    <row r="71" spans="1:29" s="46" customFormat="1" ht="60.75">
-      <c r="A71" s="45" t="s">
+      <c r="G70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O70" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="P70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R70" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="S70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="T70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W70" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X70" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA70" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB70" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" ht="60.75">
+      <c r="A71" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="B71" s="45">
+      <c r="B71" s="9">
         <v>2022</v>
       </c>
-      <c r="C71" s="45">
+      <c r="C71" s="9">
         <v>23274662</v>
       </c>
-      <c r="D71" s="45" t="s">
+      <c r="D71" s="9" t="s">
         <v>302</v>
       </c>
       <c r="E71" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="F71" s="45" t="s">
+      <c r="F71" s="9" t="s">
         <v>773</v>
       </c>
-      <c r="G71" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H71" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J71" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="K71" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="N71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P71" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q71" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R71" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="S71" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="T71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W71" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X71" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB71" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC71" s="45"/>
-    </row>
-    <row r="72" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A72" s="45" t="s">
+      <c r="G71" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="K71" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P71" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q71" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R71" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="S71" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="T71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W71" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X71" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA71" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB71" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" ht="45.75">
+      <c r="A72" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="B72" s="45">
+      <c r="B72" s="9">
         <v>2022</v>
       </c>
-      <c r="C72" s="45">
+      <c r="C72" s="9">
         <v>15249050</v>
       </c>
-      <c r="D72" s="45" t="s">
+      <c r="D72" s="9" t="s">
         <v>308</v>
       </c>
       <c r="E72" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="F72" s="45" t="s">
+      <c r="F72" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="G72" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H72" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J72" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K72" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="N72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P72" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q72" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="S72" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="T72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA72" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB72" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC72" s="45"/>
-    </row>
-    <row r="73" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A73" s="45" t="s">
+      <c r="G72" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K72" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P72" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q72" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="S72" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="T72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z72" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA72" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB72" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" ht="45.75">
+      <c r="A73" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="B73" s="45">
+      <c r="B73" s="9">
         <v>2022</v>
       </c>
-      <c r="C73" s="45">
+      <c r="C73" s="9">
         <v>1403664</v>
       </c>
-      <c r="D73" s="45" t="s">
+      <c r="D73" s="9" t="s">
         <v>311</v>
       </c>
       <c r="E73" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="F73" s="45" t="s">
+      <c r="F73" s="9" t="s">
         <v>772</v>
       </c>
-      <c r="G73" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H73" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J73" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="K73" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M73" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="N73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P73" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Q73" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="S73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="T73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U73" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="V73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y73" s="45" t="s">
+      <c r="G73" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="K73" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P73" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Q73" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="S73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="T73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U73" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="V73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y73" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="Z73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB73" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC73" s="45"/>
-    </row>
-    <row r="74" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A74" s="45" t="s">
+      <c r="Z73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA73" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB73" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" ht="45.75">
+      <c r="A74" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="B74" s="45">
+      <c r="B74" s="9">
         <v>2021</v>
       </c>
-      <c r="C74" s="45">
+      <c r="C74" s="9">
         <v>21693536</v>
       </c>
-      <c r="D74" s="45" t="s">
+      <c r="D74" s="9" t="s">
         <v>314</v>
       </c>
       <c r="E74" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F74" s="45" t="s">
+      <c r="F74" s="9" t="s">
         <v>777</v>
       </c>
-      <c r="G74" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H74" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J74" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="K74" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M74" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P74" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q74" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="S74" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="T74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W74" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB74" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC74" s="45"/>
-    </row>
-    <row r="75" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A75" s="45" t="s">
+      <c r="G74" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="K74" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P74" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q74" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="S74" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="T74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W74" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA74" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB74" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" ht="45.75">
+      <c r="A75" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="B75" s="45">
+      <c r="B75" s="9">
         <v>2021</v>
       </c>
-      <c r="C75" s="45">
+      <c r="C75" s="9">
         <v>23274662</v>
       </c>
-      <c r="D75" s="45" t="s">
+      <c r="D75" s="9" t="s">
         <v>320</v>
       </c>
       <c r="E75" s="29" t="s">
         <v>321</v>
       </c>
-      <c r="F75" s="45" t="s">
+      <c r="F75" s="9" t="s">
         <v>773</v>
       </c>
-      <c r="G75" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H75" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I75" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="J75" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K75" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M75" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="N75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P75" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q75" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="S75" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="T75" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="U75" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="V75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB75" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC75" s="45"/>
-    </row>
-    <row r="76" spans="1:29" s="46" customFormat="1" ht="60.75">
-      <c r="A76" s="45" t="s">
+      <c r="G75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="S75" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="T75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="V75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA75" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB75" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" ht="60.75">
+      <c r="A76" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="B76" s="45">
+      <c r="B76" s="9">
         <v>2021</v>
       </c>
-      <c r="C76" s="45">
+      <c r="C76" s="9">
         <v>8908044</v>
       </c>
-      <c r="D76" s="45" t="s">
+      <c r="D76" s="9" t="s">
         <v>323</v>
       </c>
       <c r="E76" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="F76" s="45" t="s">
+      <c r="F76" s="9" t="s">
         <v>772</v>
       </c>
-      <c r="G76" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H76" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J76" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K76" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M76" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="N76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P76" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q76" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R76" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="S76" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="T76" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="U76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="X76" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB76" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC76" s="45"/>
-    </row>
-    <row r="77" spans="1:29" s="46" customFormat="1" ht="63" customHeight="1">
-      <c r="A77" s="45" t="s">
+      <c r="G76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="S76" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="T76" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X76" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB76" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" ht="63" customHeight="1">
+      <c r="A77" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="B77" s="45">
+      <c r="B77" s="9">
         <v>2022</v>
       </c>
-      <c r="C77" s="45">
+      <c r="C77" s="9">
         <v>19324537</v>
       </c>
-      <c r="D77" s="45" t="s">
+      <c r="D77" s="9" t="s">
         <v>326</v>
       </c>
       <c r="E77" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="F77" s="45" t="s">
+      <c r="F77" s="9" t="s">
         <v>778</v>
       </c>
-      <c r="G77" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H77" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J77" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K77" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M77" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P77" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q77" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R77" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="S77" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="T77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W77" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X77" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB77" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC77" s="45"/>
-    </row>
-    <row r="78" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A78" s="45" t="s">
+      <c r="G77" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K77" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P77" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q77" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R77" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="S77" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="T77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W77" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X77" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA77" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB77" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" ht="45.75">
+      <c r="A78" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="B78" s="45">
+      <c r="B78" s="9">
         <v>2022</v>
       </c>
-      <c r="C78" s="45">
+      <c r="C78" s="9">
         <v>13191578</v>
       </c>
-      <c r="D78" s="45" t="s">
+      <c r="D78" s="9" t="s">
         <v>329</v>
       </c>
       <c r="E78" s="29" t="s">
         <v>330</v>
       </c>
-      <c r="F78" s="45" t="s">
+      <c r="F78" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="G78" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H78" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J78" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K78" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M78" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P78" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q78" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R78" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="S78" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="T78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W78" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X78" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB78" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC78" s="45"/>
-    </row>
-    <row r="79" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A79" s="45" t="s">
+      <c r="G78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="S78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="T78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X78" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA78" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB78" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" ht="45.75">
+      <c r="A79" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="B79" s="45">
+      <c r="B79" s="9">
         <v>2022</v>
       </c>
-      <c r="C79" s="45">
+      <c r="C79" s="9">
         <v>15361284</v>
       </c>
-      <c r="D79" s="45" t="s">
+      <c r="D79" s="9" t="s">
         <v>332</v>
       </c>
       <c r="E79" s="29" t="s">
         <v>333</v>
       </c>
-      <c r="F79" s="45" t="s">
+      <c r="F79" s="9" t="s">
         <v>772</v>
       </c>
-      <c r="G79" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H79" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="J79" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K79" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M79" s="45" t="s">
-        <v>728</v>
-      </c>
-      <c r="N79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O79" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P79" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q79" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R79" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="S79" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="T79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="U79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W79" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X79" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB79" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC79" s="45"/>
-    </row>
-    <row r="80" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A80" s="45" t="s">
+      <c r="G79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="P79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="S79" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="T79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W79" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X79" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA79" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB79" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" ht="45.75">
+      <c r="A80" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="B80" s="45">
+      <c r="B80" s="9">
         <v>2022</v>
       </c>
-      <c r="C80" s="45">
+      <c r="C80" s="9">
         <v>189480</v>
       </c>
-      <c r="D80" s="45" t="s">
+      <c r="D80" s="9" t="s">
         <v>335</v>
       </c>
       <c r="E80" s="29" t="s">
         <v>336</v>
       </c>
-      <c r="F80" s="45" t="s">
+      <c r="F80" s="9" t="s">
         <v>775</v>
       </c>
-      <c r="G80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="K80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L80" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="N80" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="S80" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="T80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="U80" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="V80" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W80" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X80" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y80" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z80" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA80" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB80" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC80" s="45"/>
-    </row>
-    <row r="81" spans="1:29" s="46" customFormat="1" ht="45.75">
-      <c r="A81" s="45" t="s">
+      <c r="G80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L80" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N80" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="P80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="S80" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="T80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U80" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="V80" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W80" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X80" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y80" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z80" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA80" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB80" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" ht="45.75">
+      <c r="A81" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="B81" s="45">
+      <c r="B81" s="9">
         <v>2021</v>
       </c>
-      <c r="C81" s="45">
+      <c r="C81" s="9">
         <v>15361284</v>
       </c>
-      <c r="D81" s="45" t="s">
+      <c r="D81" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="E81" s="45" t="s">
+      <c r="E81" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="F81" s="45" t="s">
+      <c r="F81" s="9" t="s">
         <v>771</v>
       </c>
-      <c r="G81" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="H81" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I81" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J81" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="K81" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="L81" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="M81" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="N81" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="O81" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="P81" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q81" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R81" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="S81" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="T81" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="U81" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="V81" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="W81" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="X81" s="45" t="s">
-        <v>729</v>
-      </c>
-      <c r="Y81" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z81" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA81" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB81" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC81" s="45"/>
-    </row>
-    <row r="82" spans="1:29" ht="60.75">
+      <c r="G81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="K81" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M81" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="N81" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="O81" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R81" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="S81" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="T81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="U81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="V81" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W81" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X81" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="Y81" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z81" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA81" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB81" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" ht="60.75">
       <c r="A82" s="9" t="s">
         <v>343</v>
       </c>
@@ -47277,7 +47283,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="45.75">
+    <row r="83" spans="1:28" ht="45.75">
       <c r="A83" s="9" t="s">
         <v>346</v>
       </c>
@@ -47315,7 +47321,7 @@
         <v>67</v>
       </c>
       <c r="M83" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N83" s="26" t="s">
         <v>67</v>
@@ -47363,7 +47369,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="45.75">
+    <row r="84" spans="1:28" ht="45.75">
       <c r="A84" s="9" t="s">
         <v>352</v>
       </c>
@@ -47449,7 +47455,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="45.75">
+    <row r="85" spans="1:28" ht="45.75">
       <c r="A85" s="9" t="s">
         <v>361</v>
       </c>
@@ -47535,7 +47541,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="60.75">
+    <row r="86" spans="1:28" ht="60.75">
       <c r="A86" s="9" t="s">
         <v>364</v>
       </c>
@@ -47573,7 +47579,7 @@
         <v>67</v>
       </c>
       <c r="M86" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N86" s="26" t="s">
         <v>67</v>
@@ -47621,7 +47627,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="45.75">
+    <row r="87" spans="1:28" ht="45.75">
       <c r="A87" s="9" t="s">
         <v>367</v>
       </c>
@@ -47707,7 +47713,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="45.75">
+    <row r="88" spans="1:28" ht="45.75">
       <c r="A88" s="9" t="s">
         <v>371</v>
       </c>
@@ -47793,7 +47799,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="43.7">
+    <row r="89" spans="1:28" ht="43.7">
       <c r="A89" s="9" t="s">
         <v>374</v>
       </c>
@@ -47879,7 +47885,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="45.75">
+    <row r="90" spans="1:28" ht="45.75">
       <c r="A90" s="9" t="s">
         <v>386</v>
       </c>
@@ -47917,7 +47923,7 @@
         <v>67</v>
       </c>
       <c r="M90" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N90" s="26" t="s">
         <v>67</v>
@@ -47965,7 +47971,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="30.75">
+    <row r="91" spans="1:28" ht="30.75">
       <c r="A91" s="9" t="s">
         <v>410</v>
       </c>
@@ -48051,7 +48057,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="30.75">
+    <row r="92" spans="1:28" ht="30.75">
       <c r="A92" s="9" t="s">
         <v>416</v>
       </c>
@@ -48137,7 +48143,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="30.75">
+    <row r="93" spans="1:28" ht="30.75">
       <c r="A93" s="9" t="s">
         <v>422</v>
       </c>
@@ -48175,7 +48181,7 @@
         <v>67</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N93" s="26" t="s">
         <v>9</v>
@@ -48223,7 +48229,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="45.75">
+    <row r="94" spans="1:28" ht="45.75">
       <c r="A94" s="9" t="s">
         <v>425</v>
       </c>
@@ -48261,7 +48267,7 @@
         <v>67</v>
       </c>
       <c r="M94" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N94" s="26" t="s">
         <v>729</v>
@@ -48309,7 +48315,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="60.75">
+    <row r="95" spans="1:28" ht="60.75">
       <c r="A95" s="9" t="s">
         <v>431</v>
       </c>
@@ -48395,7 +48401,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="45.75">
+    <row r="96" spans="1:28" ht="45.75">
       <c r="A96" s="9" t="s">
         <v>434</v>
       </c>
@@ -48519,7 +48525,7 @@
         <v>67</v>
       </c>
       <c r="M97" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N97" s="26" t="s">
         <v>67</v>
@@ -48691,7 +48697,7 @@
         <v>67</v>
       </c>
       <c r="M99" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N99" s="26" t="s">
         <v>67</v>
@@ -48777,7 +48783,7 @@
         <v>67</v>
       </c>
       <c r="M100" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N100" s="26" t="s">
         <v>67</v>
@@ -48863,7 +48869,7 @@
         <v>67</v>
       </c>
       <c r="M101" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N101" s="26" t="s">
         <v>67</v>
@@ -48949,7 +48955,7 @@
         <v>67</v>
       </c>
       <c r="M102" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N102" s="26" t="s">
         <v>67</v>
@@ -49379,7 +49385,7 @@
         <v>67</v>
       </c>
       <c r="M107" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N107" s="26" t="s">
         <v>67</v>
@@ -49895,7 +49901,7 @@
         <v>67</v>
       </c>
       <c r="M113" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N113" s="26" t="s">
         <v>67</v>
@@ -49981,7 +49987,7 @@
         <v>67</v>
       </c>
       <c r="M114" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N114" s="26" t="s">
         <v>729</v>
@@ -50153,7 +50159,7 @@
         <v>67</v>
       </c>
       <c r="M116" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N116" s="26" t="s">
         <v>67</v>
@@ -50201,7 +50207,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="58.35">
+    <row r="117" spans="1:28" ht="60.75">
       <c r="A117" s="9" t="s">
         <v>566</v>
       </c>
@@ -50239,7 +50245,7 @@
         <v>729</v>
       </c>
       <c r="M117" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N117" s="26" t="s">
         <v>67</v>
@@ -50459,7 +50465,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="43.7">
+    <row r="120" spans="1:28" ht="45.75">
       <c r="A120" s="9" t="s">
         <v>596</v>
       </c>
@@ -50497,7 +50503,7 @@
         <v>9</v>
       </c>
       <c r="M120" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N120" s="26" t="s">
         <v>67</v>
@@ -50803,7 +50809,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:28" ht="43.7">
+    <row r="124" spans="1:28" ht="45.75">
       <c r="A124" s="9" t="s">
         <v>620</v>
       </c>
@@ -50841,7 +50847,7 @@
         <v>9</v>
       </c>
       <c r="M124" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N124" s="26" t="s">
         <v>67</v>
@@ -50889,7 +50895,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="125" spans="1:28" ht="43.7">
+    <row r="125" spans="1:28" ht="45.75">
       <c r="A125" s="9" t="s">
         <v>623</v>
       </c>
@@ -50927,7 +50933,7 @@
         <v>67</v>
       </c>
       <c r="M125" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N125" s="26" t="s">
         <v>67</v>
@@ -50975,7 +50981,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="126" spans="1:28" ht="43.7">
+    <row r="126" spans="1:28" ht="60.75">
       <c r="A126" s="9" t="s">
         <v>629</v>
       </c>
@@ -51013,7 +51019,7 @@
         <v>9</v>
       </c>
       <c r="M126" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N126" s="26" t="s">
         <v>67</v>
@@ -51061,7 +51067,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="127" spans="1:28" ht="58.35">
+    <row r="127" spans="1:28" ht="60.75">
       <c r="A127" s="9" t="s">
         <v>633</v>
       </c>
@@ -51099,7 +51105,7 @@
         <v>9</v>
       </c>
       <c r="M127" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N127" s="26" t="s">
         <v>67</v>
@@ -51233,7 +51239,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="129" spans="1:28" ht="58.35">
+    <row r="129" spans="1:28" ht="60.75">
       <c r="A129" s="9" t="s">
         <v>637</v>
       </c>
@@ -51271,7 +51277,7 @@
         <v>9</v>
       </c>
       <c r="M129" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N129" s="26" t="s">
         <v>67</v>
@@ -51319,7 +51325,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="130" spans="1:28" ht="58.35">
+    <row r="130" spans="1:28" ht="60.75">
       <c r="A130" s="9" t="s">
         <v>639</v>
       </c>
@@ -51357,7 +51363,7 @@
         <v>9</v>
       </c>
       <c r="M130" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N130" s="26" t="s">
         <v>729</v>
@@ -51749,7 +51755,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="135" spans="1:28" s="9" customFormat="1" ht="43.7">
+    <row r="135" spans="1:28" s="9" customFormat="1" ht="45.75">
       <c r="A135" s="9" t="s">
         <v>651</v>
       </c>
@@ -51787,7 +51793,7 @@
         <v>9</v>
       </c>
       <c r="M135" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N135" s="26" t="s">
         <v>67</v>
@@ -52007,7 +52013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="138" spans="1:28" s="9" customFormat="1" ht="43.7">
+    <row r="138" spans="1:28" s="9" customFormat="1" ht="45.75">
       <c r="A138" s="9" t="s">
         <v>657</v>
       </c>
@@ -52045,7 +52051,7 @@
         <v>9</v>
       </c>
       <c r="M138" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N138" s="26" t="s">
         <v>67</v>
@@ -52265,7 +52271,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="141" spans="1:28" s="9" customFormat="1" ht="58.35">
+    <row r="141" spans="1:28" s="9" customFormat="1" ht="60.75">
       <c r="A141" s="9" t="s">
         <v>663</v>
       </c>
@@ -52303,7 +52309,7 @@
         <v>9</v>
       </c>
       <c r="M141" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N141" s="26" t="s">
         <v>67</v>
@@ -52523,7 +52529,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="144" spans="1:28" s="9" customFormat="1" ht="43.7">
+    <row r="144" spans="1:28" s="9" customFormat="1" ht="45.75">
       <c r="A144" s="9" t="s">
         <v>669</v>
       </c>
@@ -52561,7 +52567,7 @@
         <v>67</v>
       </c>
       <c r="M144" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N144" s="26" t="s">
         <v>67</v>
@@ -52609,7 +52615,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="145" spans="1:28" s="9" customFormat="1" ht="29.1">
+    <row r="145" spans="1:28" s="9" customFormat="1" ht="30.75">
       <c r="A145" s="9" t="s">
         <v>671</v>
       </c>
@@ -52647,7 +52653,7 @@
         <v>9</v>
       </c>
       <c r="M145" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N145" s="26" t="s">
         <v>67</v>
@@ -52695,7 +52701,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="146" spans="1:28" s="9" customFormat="1" ht="43.7">
+    <row r="146" spans="1:28" s="9" customFormat="1" ht="45.75">
       <c r="A146" s="9" t="s">
         <v>673</v>
       </c>
@@ -52733,7 +52739,7 @@
         <v>9</v>
       </c>
       <c r="M146" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N146" s="26" t="s">
         <v>67</v>
@@ -52781,7 +52787,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="147" spans="1:28" s="9" customFormat="1" ht="58.35">
+    <row r="147" spans="1:28" s="9" customFormat="1" ht="60.75">
       <c r="A147" s="9" t="s">
         <v>675</v>
       </c>
@@ -52819,7 +52825,7 @@
         <v>67</v>
       </c>
       <c r="M147" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N147" s="26" t="s">
         <v>67</v>
@@ -52867,7 +52873,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="148" spans="1:28" s="9" customFormat="1" ht="58.35">
+    <row r="148" spans="1:28" s="9" customFormat="1" ht="60.75">
       <c r="A148" s="9" t="s">
         <v>677</v>
       </c>
@@ -52905,7 +52911,7 @@
         <v>9</v>
       </c>
       <c r="M148" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N148" s="26" t="s">
         <v>67</v>
@@ -52953,7 +52959,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="149" spans="1:28" s="9" customFormat="1" ht="43.7">
+    <row r="149" spans="1:28" s="9" customFormat="1" ht="60.75">
       <c r="A149" s="9" t="s">
         <v>679</v>
       </c>
@@ -52991,7 +52997,7 @@
         <v>9</v>
       </c>
       <c r="M149" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N149" s="26" t="s">
         <v>67</v>
@@ -53125,7 +53131,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="151" spans="1:28" s="9" customFormat="1" ht="43.7">
+    <row r="151" spans="1:28" s="9" customFormat="1" ht="45.75">
       <c r="A151" s="9" t="s">
         <v>683</v>
       </c>
@@ -53163,7 +53169,7 @@
         <v>67</v>
       </c>
       <c r="M151" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N151" s="26" t="s">
         <v>67</v>
@@ -53211,7 +53217,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="152" spans="1:28" s="9" customFormat="1" ht="58.35">
+    <row r="152" spans="1:28" s="9" customFormat="1" ht="60.75">
       <c r="A152" s="9" t="s">
         <v>685</v>
       </c>
@@ -53249,7 +53255,7 @@
         <v>9</v>
       </c>
       <c r="M152" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N152" s="26" t="s">
         <v>67</v>
@@ -53297,7 +53303,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="153" spans="1:28" s="9" customFormat="1" ht="58.35">
+    <row r="153" spans="1:28" s="9" customFormat="1" ht="60.75">
       <c r="A153" s="9" t="s">
         <v>687</v>
       </c>
@@ -53335,7 +53341,7 @@
         <v>67</v>
       </c>
       <c r="M153" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N153" s="26" t="s">
         <v>729</v>
@@ -53641,7 +53647,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="157" spans="1:28" s="9" customFormat="1" ht="58.35">
+    <row r="157" spans="1:28" s="9" customFormat="1" ht="60.75">
       <c r="A157" s="9" t="s">
         <v>697</v>
       </c>
@@ -53679,7 +53685,7 @@
         <v>67</v>
       </c>
       <c r="M157" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N157" s="26" t="s">
         <v>729</v>
@@ -53727,7 +53733,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" spans="1:28" s="9" customFormat="1" ht="43.7">
+    <row r="158" spans="1:28" s="9" customFormat="1" ht="45.75">
       <c r="A158" s="9" t="s">
         <v>701</v>
       </c>
@@ -53765,7 +53771,7 @@
         <v>67</v>
       </c>
       <c r="M158" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N158" s="26" t="s">
         <v>67</v>
@@ -53813,7 +53819,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="159" spans="1:28" s="9" customFormat="1" ht="43.7">
+    <row r="159" spans="1:28" s="9" customFormat="1" ht="45.75">
       <c r="A159" s="9" t="s">
         <v>703</v>
       </c>
@@ -53851,7 +53857,7 @@
         <v>9</v>
       </c>
       <c r="M159" s="9" t="s">
-        <v>728</v>
+        <v>67</v>
       </c>
       <c r="N159" s="26" t="s">
         <v>67</v>
@@ -53901,6 +53907,25 @@
     </row>
     <row r="160" spans="1:28" ht="15"/>
   </sheetData>
+  <autoFilter ref="A1:AC159" xr:uid="{EFADC3EE-BC49-4A15-B222-71FCC48B444F}">
+    <filterColumn colId="6" showButton="0"/>
+    <filterColumn colId="7" showButton="0"/>
+    <filterColumn colId="8" showButton="0"/>
+    <filterColumn colId="9" showButton="0"/>
+    <filterColumn colId="11" showButton="0"/>
+    <filterColumn colId="12" showButton="0"/>
+    <filterColumn colId="14" showButton="0"/>
+    <filterColumn colId="15" showButton="0"/>
+    <filterColumn colId="16" showButton="0"/>
+    <filterColumn colId="17" showButton="0"/>
+    <filterColumn colId="18" showButton="0"/>
+    <filterColumn colId="19" showButton="0"/>
+    <filterColumn colId="20" showButton="0"/>
+    <filterColumn colId="21" showButton="0"/>
+    <filterColumn colId="24" showButton="0"/>
+    <filterColumn colId="25" showButton="0"/>
+    <filterColumn colId="26" showButton="0"/>
+  </autoFilter>
   <mergeCells count="10">
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:N1"/>
@@ -53914,7 +53939,7 @@
     <mergeCell ref="F1:F2"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2 M3:M1048576 U3:U1048576 Y3:Z1048576" xr:uid="{56F3C0FA-0D3E-42C7-AA34-F54B881F9653}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2 Y3:Z1048576 U3:U1048576 M3:M1048576" xr:uid="{56F3C0FA-0D3E-42C7-AA34-F54B881F9653}">
       <formula1>"Yes, No, NA"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W153:W1048576 T3:T1048576 AA3:AB1048576 V3:V1048576 W3:W151" xr:uid="{89366B6F-E960-4CF6-85C2-DE3147B452D7}">
